--- a/docs/milestone 1/literature_matrix.xlsx
+++ b/docs/milestone 1/literature_matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mazen\Desktop\AAST\Research\Autonomous research\docs\milestone 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD493CFC-53F5-48C0-B36F-3C08E6B532ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C983B587-5ECE-4250-8DC9-9A79F2D47CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="215">
   <si>
     <t>18 core papers organized by dataset, detector architecture, domain shift/generalization, and safety/deployment evaluation.</t>
   </si>
@@ -585,13 +585,94 @@
   </si>
   <si>
     <t>Literature Matrix</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>Model-selection instability under external domain shift</t>
+  </si>
+  <si>
+    <t>A detector instance selected as best on the internal test set may not remain best on an external dataset; prior work rarely checks whether rankings across detector families and hyperparameter variants remain stable under direct cross-dataset evaluation without target-domain adaptation.</t>
+  </si>
+  <si>
+    <t>Chen et al. — Dynamic Supervisor for Cross-dataset Object Detection (2022)</t>
+  </si>
+  <si>
+    <t>Proposed a dynamic supervisor framework for cross-dataset object detection under inconsistent category ranges and missing annotations.</t>
+  </si>
+  <si>
+    <t>Showed that hard-label training improves annotation recall while soft-label training improves precision, and combining both improves generated annotations.</t>
+  </si>
+  <si>
+    <t>Focuses on cross-dataset training and annotation generation, not direct frozen-model external validation.</t>
+  </si>
+  <si>
+    <t>Supports the argument that cross-dataset detection is affected by label/category inconsistency and that direct robustness evaluation should be separated from adaptation/training methods.</t>
+  </si>
+  <si>
+    <t>Cross-dataset object detection settings; hard-label and soft-label submodels</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/abs/pii/S0925231221014764</t>
+  </si>
+  <si>
+    <t>Lu et al. — BSMH: Cross-dataset object detection based on box-separated multiple-head (2024)</t>
+  </si>
+  <si>
+    <t>Proposed a YOLOv8-based box-separated multiple-head module, box-separated loss, same-class-aware fusion, and global class-aware sampler for cross-dataset detection.</t>
+  </si>
+  <si>
+    <t>Cross-datasets built from COCO, WiderFace, WiderPerson, and OpenImages V4.</t>
+  </si>
+  <si>
+    <t>Showed that dataset-aware errors, false alarms, category conflicts, and sample/category imbalance affect cross-dataset detection.</t>
+  </si>
+  <si>
+    <t>It proposes a specialized training architecture and does not evaluate frozen detector families under KITTI-to-Waymo-style external validation.</t>
+  </si>
+  <si>
+    <t>Strengthens the motivation for evaluating detectors under dataset shift and analyzing false alarms/errors beyond aggregate mAP.</t>
+  </si>
+  <si>
+    <t>https://ietresearch.onlinelibrary.wiley.com/doi/10.1049/ipr2.13152</t>
+  </si>
+  <si>
+    <t>Chakraborty et al. — Towards Robust Cross-Dataset Object Detection Generalization under Domain Specificity (2026)</t>
+  </si>
+  <si>
+    <t>Studied cross-dataset object detection using setting-specific vs setting-agnostic datasets and evaluated train–test transfer across datasets.</t>
+  </si>
+  <si>
+    <t>Faster R-CNN ResNet-50 FPN; COCO, Objects365, Cityscapes, BDD100K.</t>
+  </si>
+  <si>
+    <t>Found that detectors can perform well in-distribution but degrade sharply on different benchmarks; transfer across setting types can be unstable and asymmetric.</t>
+  </si>
+  <si>
+    <t>Uses one standard detector family rather than comparing multiple detector families and hyperparameter variants. It is also an arXiv preprint.</t>
+  </si>
+  <si>
+    <t>Directly supports our external validation design and motivates testing whether internal rankings remain stable under KITTI-to-Waymo domain shift.</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2601.09497</t>
+  </si>
+  <si>
+    <t>G3 — Dependence on target-domain adaptation; G7 — External-validation transparency; G8 — Model-selection instability under external shift</t>
+  </si>
+  <si>
+    <t>G3 — Dependence on target-domain adaptation; G5 — Overreliance on aggregate accuracy; G8 — Model-selection instability under external shift</t>
+  </si>
+  <si>
+    <t>G4 — Narrow shift/task coverage; G7 — External-validation transparency; G8 — Model-selection instability under external shift</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -663,8 +744,20 @@
       <sz val="14"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +817,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -813,10 +912,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -825,9 +925,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -869,15 +966,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -914,20 +1002,8 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -942,23 +1018,63 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="9">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -1063,6 +1179,18 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1090,6 +1218,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Core Papers by Literature Group</a:t>
             </a:r>
           </a:p>
@@ -1144,7 +1273,7 @@
                   <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3</c:v>
@@ -1256,7 +1385,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1286,16 +1415,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrixTable" displayName="LiteratureMatrixTable" ref="A5:I23" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="LiteratureMatrixTable" displayName="LiteratureMatrixTable" ref="A5:I26" headerRowDxfId="8">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Main contribution" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dataset/model" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Main finding" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Limitation" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Relevance to our study" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Supported gap" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Paper" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Category" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Main contribution" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Dataset/model" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Main finding" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Limitation" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Relevance to our study" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Supported gap" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Source URL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1451,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -1466,17 +1595,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.65" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="20.85" customHeight="1">
       <c r="A2" s="40" t="s">
@@ -1496,87 +1625,87 @@
         <v>1</v>
       </c>
       <c r="B3" s="41"/>
-      <c r="C3" s="42">
-        <v>18</v>
+      <c r="C3" s="34">
+        <v>21</v>
       </c>
       <c r="D3" s="41" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="41"/>
-      <c r="F3" s="42">
+      <c r="F3" s="34">
         <v>4</v>
       </c>
       <c r="G3" s="41" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="41"/>
-      <c r="I3" s="42">
+      <c r="I3" s="34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.399999999999999">
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+    </row>
+    <row r="5" spans="1:9" ht="28.05" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="37" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="17.399999999999999">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-    </row>
-    <row r="5" spans="1:9" ht="28.05" customHeight="1">
-      <c r="A5" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="45" t="s">
+      <c r="F5" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="46" t="s">
+      <c r="I5" s="38" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="23" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1584,28 +1713,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="F7" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="26" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -1613,28 +1742,28 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="28" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -1642,28 +1771,28 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="26" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1671,28 +1800,28 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="28" t="s">
         <v>51</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -1700,28 +1829,28 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="30" t="s">
+      <c r="G11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="26" t="s">
         <v>59</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -1729,28 +1858,28 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="28" t="s">
         <v>51</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1758,28 +1887,28 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="26" t="s">
         <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -1787,28 +1916,28 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="28" t="s">
         <v>75</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -1816,28 +1945,28 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="26" t="s">
         <v>51</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -1845,28 +1974,28 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="35" t="s">
+      <c r="B16" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="28" t="s">
         <v>98</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -1874,28 +2003,28 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="G17" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="26" t="s">
         <v>106</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -1903,28 +2032,28 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="28" t="s">
         <v>114</v>
       </c>
       <c r="I18" s="3" t="s">
@@ -1932,28 +2061,28 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G19" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="26" t="s">
         <v>122</v>
       </c>
       <c r="I19" s="2" t="s">
@@ -1961,118 +2090,205 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="83.25" customHeight="1">
+      <c r="A21" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="H21" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="83.25" customHeight="1">
+      <c r="A22" s="49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="83.25" customHeight="1">
+      <c r="A23" s="51" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B23" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C23" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D23" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E23" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F23" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G23" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H23" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I23" s="53" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A21" s="28" t="s">
+    <row r="24" spans="1:9" ht="60">
+      <c r="A24" s="51" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B24" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C24" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D24" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E24" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F24" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="G24" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="H21" s="30" t="s">
+      <c r="H24" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I24" s="53" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A22" s="31" t="s">
+    <row r="25" spans="1:9" ht="60">
+      <c r="A25" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B25" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C25" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D25" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E25" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F25" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G25" s="49" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H25" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I25" s="53" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="83.25" customHeight="1">
-      <c r="A23" s="37" t="s">
+    <row r="26" spans="1:9" ht="45">
+      <c r="A26" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B26" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C26" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D26" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E26" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F26" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="G26" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="H23" s="39" t="s">
+      <c r="H26" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I26" s="55" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2084,16 +2300,21 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="G3:H3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I20" r:id="rId1" xr:uid="{5CD5EC99-8DD4-43C7-82C5-DB67F339CEFB}"/>
+    <hyperlink ref="I21" r:id="rId2" xr:uid="{A86D8C89-187A-4AB2-8ED3-86795952055B}"/>
+    <hyperlink ref="I22" r:id="rId3" xr:uid="{8B00C239-1511-494B-BD07-ECBC57D1F4F6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -2103,181 +2324,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="9">
-        <v>5</v>
+      <c r="B6" s="8">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B8" s="11">
-        <v>18</v>
+      <c r="B8" s="10">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="13" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="41.55" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="17" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="24" t="s">
+    <row r="19" spans="1:6" ht="41.55" customHeight="1">
+      <c r="A19" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="43"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A21:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
